--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/177.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/177.xlsx
@@ -426,13 +426,13 @@
         <v>6.279678414313933</v>
       </c>
       <c r="E2">
-        <v>-14.10814132595006</v>
+        <v>-10.60214240752357</v>
       </c>
       <c r="F2">
-        <v>-3.702243289764408</v>
+        <v>-3.537048605563325</v>
       </c>
       <c r="G2">
-        <v>-6.400222562467152</v>
+        <v>-5.62248603056279</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.032033535252762</v>
       </c>
       <c r="E3">
-        <v>-12.42827672196069</v>
+        <v>-11.12228293204459</v>
       </c>
       <c r="F3">
-        <v>-4.211707466568965</v>
+        <v>-3.670439780068727</v>
       </c>
       <c r="G3">
-        <v>-6.709404342016306</v>
+        <v>-5.765945210961568</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.695691682443685</v>
       </c>
       <c r="E4">
-        <v>-13.17571947082271</v>
+        <v>-11.03954771192445</v>
       </c>
       <c r="F4">
-        <v>-4.243742090770028</v>
+        <v>-3.604394875410925</v>
       </c>
       <c r="G4">
-        <v>-6.441299811518429</v>
+        <v>-4.659461575370959</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.303016124872173</v>
       </c>
       <c r="E5">
-        <v>-15.45214712668654</v>
+        <v>-12.52142743229847</v>
       </c>
       <c r="F5">
-        <v>-4.394982926070954</v>
+        <v>-3.449499283128848</v>
       </c>
       <c r="G5">
-        <v>-5.839151304471471</v>
+        <v>-4.107560528519059</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.881985986110578</v>
       </c>
       <c r="E6">
-        <v>-13.65489541947034</v>
+        <v>-12.88463369008367</v>
       </c>
       <c r="F6">
-        <v>-4.439281529670462</v>
+        <v>-3.620326037301565</v>
       </c>
       <c r="G6">
-        <v>-5.883135212506229</v>
+        <v>-4.756811477498768</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.464669311057504</v>
       </c>
       <c r="E7">
-        <v>-14.28592015854318</v>
+        <v>-13.70728533526508</v>
       </c>
       <c r="F7">
-        <v>-4.821018079902559</v>
+        <v>-3.362577863185694</v>
       </c>
       <c r="G7">
-        <v>-5.59296258544357</v>
+        <v>-3.509662761944526</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.078076271428477</v>
       </c>
       <c r="E8">
-        <v>-16.04634178665499</v>
+        <v>-12.80844211490462</v>
       </c>
       <c r="F8">
-        <v>-4.48981111287383</v>
+        <v>-3.9739933580898</v>
       </c>
       <c r="G8">
-        <v>-5.771172562368077</v>
+        <v>-3.832901117853425</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.74499281311616</v>
       </c>
       <c r="E9">
-        <v>-16.13066650115182</v>
+        <v>-13.77329237240089</v>
       </c>
       <c r="F9">
-        <v>-4.852419831407882</v>
+        <v>-4.088631122963224</v>
       </c>
       <c r="G9">
-        <v>-6.302442289419238</v>
+        <v>-3.039108440083598</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.493034541929753</v>
       </c>
       <c r="E10">
-        <v>-14.68986909697539</v>
+        <v>-14.82580935821165</v>
       </c>
       <c r="F10">
-        <v>-5.059441270878521</v>
+        <v>-4.311238295117534</v>
       </c>
       <c r="G10">
-        <v>-5.156006990260705</v>
+        <v>-3.329757785703912</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.338787464261219</v>
       </c>
       <c r="E11">
-        <v>-16.51395201268703</v>
+        <v>-14.4543114645184</v>
       </c>
       <c r="F11">
-        <v>-4.727521907883384</v>
+        <v>-3.717886179798874</v>
       </c>
       <c r="G11">
-        <v>-4.252817335145661</v>
+        <v>-3.106620395265955</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.288682561873476</v>
       </c>
       <c r="E12">
-        <v>-16.70597742450829</v>
+        <v>-15.22226820063517</v>
       </c>
       <c r="F12">
-        <v>-4.606103127450644</v>
+        <v>-4.444583081048379</v>
       </c>
       <c r="G12">
-        <v>-4.69066346707859</v>
+        <v>-2.598554281899546</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.334700434174745</v>
       </c>
       <c r="E13">
-        <v>-17.99925525941085</v>
+        <v>-16.19204543785179</v>
       </c>
       <c r="F13">
-        <v>-4.541538515341645</v>
+        <v>-3.785996204391855</v>
       </c>
       <c r="G13">
-        <v>-2.949107949052971</v>
+        <v>-2.493626541032345</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.472759518471022</v>
       </c>
       <c r="E14">
-        <v>-18.40748813425432</v>
+        <v>-15.94467754518279</v>
       </c>
       <c r="F14">
-        <v>-4.919244229791719</v>
+        <v>-3.538442747902237</v>
       </c>
       <c r="G14">
-        <v>-3.435268182586024</v>
+        <v>-2.301356677202553</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.688307061640979</v>
       </c>
       <c r="E15">
-        <v>-19.6014157779026</v>
+        <v>-16.53721478366444</v>
       </c>
       <c r="F15">
-        <v>-4.93023418012466</v>
+        <v>-4.170156557644543</v>
       </c>
       <c r="G15">
-        <v>-4.209012196570025</v>
+        <v>-1.325248946039522</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.962190491016217</v>
       </c>
       <c r="E16">
-        <v>-19.28859785040074</v>
+        <v>-17.1477119500605</v>
       </c>
       <c r="F16">
-        <v>-4.732373655761581</v>
+        <v>-3.777057291748246</v>
       </c>
       <c r="G16">
-        <v>-2.760022830031958</v>
+        <v>-0.297476841190625</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.268787449416692</v>
       </c>
       <c r="E17">
-        <v>-19.9510456706128</v>
+        <v>-17.60429534188386</v>
       </c>
       <c r="F17">
-        <v>-4.466927463371493</v>
+        <v>-3.910948800164938</v>
       </c>
       <c r="G17">
-        <v>-2.144185217180114</v>
+        <v>-0.2857740627093013</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.591927070231451</v>
       </c>
       <c r="E18">
-        <v>-20.86929793057014</v>
+        <v>-19.27226817312908</v>
       </c>
       <c r="F18">
-        <v>-4.230837783369218</v>
+        <v>-3.886823427925805</v>
       </c>
       <c r="G18">
-        <v>-0.8049106403590339</v>
+        <v>-0.08317529679698321</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.913096002075803</v>
       </c>
       <c r="E19">
-        <v>-21.52196424692563</v>
+        <v>-18.67814596874476</v>
       </c>
       <c r="F19">
-        <v>-4.64286110258247</v>
+        <v>-3.478968453483441</v>
       </c>
       <c r="G19">
-        <v>-2.145665031036168</v>
+        <v>-0.07491879622204088</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.214281052629775</v>
       </c>
       <c r="E20">
-        <v>-22.37395134672874</v>
+        <v>-20.08353070618121</v>
       </c>
       <c r="F20">
-        <v>-4.453230408366204</v>
+        <v>-3.157991823879285</v>
       </c>
       <c r="G20">
-        <v>-1.286800270146427</v>
+        <v>-0.0890382729470325</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.475392262808168</v>
       </c>
       <c r="E21">
-        <v>-21.5431393913855</v>
+        <v>-19.54388604410915</v>
       </c>
       <c r="F21">
-        <v>-3.890980175553053</v>
+        <v>-3.137819420886312</v>
       </c>
       <c r="G21">
-        <v>-1.631209564778965</v>
+        <v>-0.4167690391527229</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.68539797561385</v>
       </c>
       <c r="E22">
-        <v>-22.28866206726827</v>
+        <v>-21.26529034017088</v>
       </c>
       <c r="F22">
-        <v>-3.542893565957479</v>
+        <v>-2.927264994442734</v>
       </c>
       <c r="G22">
-        <v>-1.51494982653084</v>
+        <v>-0.1284966652296058</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.833788346315487</v>
       </c>
       <c r="E23">
-        <v>-21.70236053749519</v>
+        <v>-20.27763468757198</v>
       </c>
       <c r="F23">
-        <v>-3.642566045331926</v>
+        <v>-2.756265939850234</v>
       </c>
       <c r="G23">
-        <v>-1.638396759144723</v>
+        <v>0.4687191289638378</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.911630226531691</v>
       </c>
       <c r="E24">
-        <v>-24.06847462108093</v>
+        <v>-20.37371532059272</v>
       </c>
       <c r="F24">
-        <v>-3.417729736496681</v>
+        <v>-2.599840352975187</v>
       </c>
       <c r="G24">
-        <v>-0.9632639651389927</v>
+        <v>-0.125374820786073</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.910048894636704</v>
       </c>
       <c r="E25">
-        <v>-23.32327799532671</v>
+        <v>-22.12677817844207</v>
       </c>
       <c r="F25">
-        <v>-3.445053435278023</v>
+        <v>-2.534788660833342</v>
       </c>
       <c r="G25">
-        <v>-1.412117660989998</v>
+        <v>0.4590225410793125</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.828910774336648</v>
       </c>
       <c r="E26">
-        <v>-24.93987981742892</v>
+        <v>-22.20544682890332</v>
       </c>
       <c r="F26">
-        <v>-2.954807382218414</v>
+        <v>-2.619463548380105</v>
       </c>
       <c r="G26">
-        <v>-1.509732406760948</v>
+        <v>-0.1773239013883165</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.669847948507502</v>
       </c>
       <c r="E27">
-        <v>-23.62303127531644</v>
+        <v>-21.43797463950537</v>
       </c>
       <c r="F27">
-        <v>-3.570726710691542</v>
+        <v>-2.382709517720783</v>
       </c>
       <c r="G27">
-        <v>-2.703177452577133</v>
+        <v>-0.1817236164100079</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.436743082776687</v>
       </c>
       <c r="E28">
-        <v>-23.60304711952059</v>
+        <v>-20.39290246496322</v>
       </c>
       <c r="F28">
-        <v>-3.372050244436706</v>
+        <v>-2.854371148098585</v>
       </c>
       <c r="G28">
-        <v>-1.538328899129173</v>
+        <v>-0.6878431289993263</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.134176648929015</v>
       </c>
       <c r="E29">
-        <v>-23.00307412671835</v>
+        <v>-20.75978131516865</v>
       </c>
       <c r="F29">
-        <v>-3.243760156397744</v>
+        <v>-2.169332015168464</v>
       </c>
       <c r="G29">
-        <v>-1.171891234478324</v>
+        <v>-0.6939477749737424</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.775548616165509</v>
       </c>
       <c r="E30">
-        <v>-24.56788379159483</v>
+        <v>-20.24697691854005</v>
       </c>
       <c r="F30">
-        <v>-2.628586358587135</v>
+        <v>-2.51885418547309</v>
       </c>
       <c r="G30">
-        <v>-1.745919967714712</v>
+        <v>-1.250695460495135</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.374671919980498</v>
       </c>
       <c r="E31">
-        <v>-22.7421525113444</v>
+        <v>-19.91379444342571</v>
       </c>
       <c r="F31">
-        <v>-2.567016294639256</v>
+        <v>-2.280001900182478</v>
       </c>
       <c r="G31">
-        <v>-2.955649587038571</v>
+        <v>-0.9383587310470555</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.946277643572988</v>
       </c>
       <c r="E32">
-        <v>-23.38943900057878</v>
+        <v>-20.4013888252536</v>
       </c>
       <c r="F32">
-        <v>-2.950109710677138</v>
+        <v>-1.881538126985652</v>
       </c>
       <c r="G32">
-        <v>-2.800970967807204</v>
+        <v>-0.9301717519284379</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.50369556052711</v>
       </c>
       <c r="E33">
-        <v>-22.37217165644372</v>
+        <v>-20.62041299910858</v>
       </c>
       <c r="F33">
-        <v>-2.939221649534741</v>
+        <v>-2.123864585163605</v>
       </c>
       <c r="G33">
-        <v>-1.321276291392397</v>
+        <v>-1.168928296220676</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.066602191732453</v>
       </c>
       <c r="E34">
-        <v>-22.59964596279702</v>
+        <v>-19.07840420086072</v>
       </c>
       <c r="F34">
-        <v>-3.033373060169531</v>
+        <v>-2.297998182008298</v>
       </c>
       <c r="G34">
-        <v>-2.145939806315928</v>
+        <v>-1.148912737890242</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.651592191218231</v>
       </c>
       <c r="E35">
-        <v>-21.78852381243913</v>
+        <v>-19.11354063068623</v>
       </c>
       <c r="F35">
-        <v>-2.294959730374829</v>
+        <v>-2.037182563399859</v>
       </c>
       <c r="G35">
-        <v>-4.101131449081794</v>
+        <v>-1.029445081014563</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.272114437537559</v>
       </c>
       <c r="E36">
-        <v>-21.7337745616864</v>
+        <v>-18.70034907680436</v>
       </c>
       <c r="F36">
-        <v>-2.583606008615122</v>
+        <v>-1.789007002990738</v>
       </c>
       <c r="G36">
-        <v>-2.631318751101712</v>
+        <v>-2.27943093409596</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.936425032334102</v>
       </c>
       <c r="E37">
-        <v>-20.6353026216458</v>
+        <v>-19.02672978395919</v>
       </c>
       <c r="F37">
-        <v>-2.315008706624786</v>
+        <v>-2.087779244362853</v>
       </c>
       <c r="G37">
-        <v>-3.95374927221898</v>
+        <v>-1.582951742453009</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.655110185760273</v>
       </c>
       <c r="E38">
-        <v>-21.00171503902843</v>
+        <v>-17.78748117244215</v>
       </c>
       <c r="F38">
-        <v>-2.148622001731074</v>
+        <v>-1.614224794469654</v>
       </c>
       <c r="G38">
-        <v>-2.268605450182543</v>
+        <v>-1.1406562373153</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.432944141643961</v>
       </c>
       <c r="E39">
-        <v>-19.65482007187505</v>
+        <v>-16.9934449545152</v>
       </c>
       <c r="F39">
-        <v>-2.758664891848742</v>
+        <v>-1.361800537651574</v>
       </c>
       <c r="G39">
-        <v>-3.212504883794005</v>
+        <v>-1.223744309259928</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.26936069009481</v>
       </c>
       <c r="E40">
-        <v>-19.46565665562665</v>
+        <v>-17.60079935994994</v>
       </c>
       <c r="F40">
-        <v>-2.78431280337422</v>
+        <v>-1.974373261817392</v>
       </c>
       <c r="G40">
-        <v>-2.837880240024538</v>
+        <v>-1.972477151694735</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.158512548486631</v>
       </c>
       <c r="E41">
-        <v>-18.05879110718969</v>
+        <v>-16.51687740689599</v>
       </c>
       <c r="F41">
-        <v>-2.316135286292593</v>
+        <v>-1.850056852209659</v>
       </c>
       <c r="G41">
-        <v>-2.863679321412078</v>
+        <v>-1.514744572707405</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.096183139352108</v>
       </c>
       <c r="E42">
-        <v>-19.65456194885662</v>
+        <v>-15.87705384282625</v>
       </c>
       <c r="F42">
-        <v>-3.107307335971595</v>
+        <v>-1.778164502055496</v>
       </c>
       <c r="G42">
-        <v>-2.826998476836954</v>
+        <v>-2.090597416535931</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.075283976107681</v>
       </c>
       <c r="E43">
-        <v>-18.02149459526252</v>
+        <v>-15.58787907811844</v>
       </c>
       <c r="F43">
-        <v>-2.606676869150491</v>
+        <v>-1.760086211856799</v>
       </c>
       <c r="G43">
-        <v>-3.258134132961779</v>
+        <v>-2.240859768017911</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.086397516511799</v>
       </c>
       <c r="E44">
-        <v>-17.03164716124391</v>
+        <v>-15.20240631363753</v>
       </c>
       <c r="F44">
-        <v>-2.70323385872301</v>
+        <v>-1.649635015837124</v>
       </c>
       <c r="G44">
-        <v>-2.853098817868568</v>
+        <v>-1.046325552719307</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.11886837473741</v>
       </c>
       <c r="E45">
-        <v>-16.41962389910726</v>
+        <v>-14.36900859963592</v>
       </c>
       <c r="F45">
-        <v>-2.616723309011644</v>
+        <v>-1.605377002240352</v>
       </c>
       <c r="G45">
-        <v>-2.858826061651507</v>
+        <v>-2.02101305984599</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.165314414375199</v>
       </c>
       <c r="E46">
-        <v>-16.02319222752778</v>
+        <v>-13.45278056756</v>
       </c>
       <c r="F46">
-        <v>-2.252813225287793</v>
+        <v>-1.640660483395195</v>
       </c>
       <c r="G46">
-        <v>-3.323421401541747</v>
+        <v>-1.27256492432756</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.219204468474614</v>
       </c>
       <c r="E47">
-        <v>-13.82895184642916</v>
+        <v>-14.01365924425402</v>
       </c>
       <c r="F47">
-        <v>-2.592743729435404</v>
+        <v>-2.125997631225814</v>
       </c>
       <c r="G47">
-        <v>-2.764319918141932</v>
+        <v>-2.088293276840599</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.274385093563959</v>
       </c>
       <c r="E48">
-        <v>-14.24551258497274</v>
+        <v>-13.05398956102253</v>
       </c>
       <c r="F48">
-        <v>-2.133271525389796</v>
+        <v>-1.963170421061932</v>
       </c>
       <c r="G48">
-        <v>-3.339216014309609</v>
+        <v>-1.763836640173247</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.325264159542076</v>
       </c>
       <c r="E49">
-        <v>-15.24018737228352</v>
+        <v>-13.16536285076717</v>
       </c>
       <c r="F49">
-        <v>-2.476664605281109</v>
+        <v>-1.715470343542018</v>
       </c>
       <c r="G49">
-        <v>-3.191264423614041</v>
+        <v>-1.844130611682731</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.368801392688946</v>
       </c>
       <c r="E50">
-        <v>-13.52995029312471</v>
+        <v>-12.32034960093588</v>
       </c>
       <c r="F50">
-        <v>-2.44142668433342</v>
+        <v>-1.783285469339602</v>
       </c>
       <c r="G50">
-        <v>-3.462331892369566</v>
+        <v>-1.111963739126437</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.403074031702724</v>
       </c>
       <c r="E51">
-        <v>-14.1061578543347</v>
+        <v>-12.01103671231597</v>
       </c>
       <c r="F51">
-        <v>-2.770679532658946</v>
+        <v>-1.933268842923078</v>
       </c>
       <c r="G51">
-        <v>-3.63369566111886</v>
+        <v>-2.814054243778403</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.425799116995005</v>
       </c>
       <c r="E52">
-        <v>-12.60466078455945</v>
+        <v>-11.55128791716124</v>
       </c>
       <c r="F52">
-        <v>-2.300873445263415</v>
+        <v>-1.561690562151512</v>
       </c>
       <c r="G52">
-        <v>-3.878186070285116</v>
+        <v>-1.584391829762592</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.434440488649723</v>
       </c>
       <c r="E53">
-        <v>-11.13262596667811</v>
+        <v>-9.761440264947586</v>
       </c>
       <c r="F53">
-        <v>-2.053890733914325</v>
+        <v>-1.876800693809041</v>
       </c>
       <c r="G53">
-        <v>-3.927053032990298</v>
+        <v>-2.108328698444268</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.427209582917769</v>
       </c>
       <c r="E54">
-        <v>-12.81011765028746</v>
+        <v>-10.35298123914754</v>
       </c>
       <c r="F54">
-        <v>-2.270779685887111</v>
+        <v>-1.837227926242503</v>
       </c>
       <c r="G54">
-        <v>-3.988811260025402</v>
+        <v>-1.954202940317959</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.402249286262159</v>
       </c>
       <c r="E55">
-        <v>-11.7453239714419</v>
+        <v>-11.04754046854799</v>
       </c>
       <c r="F55">
-        <v>-2.17879362764324</v>
+        <v>-1.461328881097935</v>
       </c>
       <c r="G55">
-        <v>-3.553649980524822</v>
+        <v>-2.762019088992139</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.357206473951497</v>
       </c>
       <c r="E56">
-        <v>-10.84584676472036</v>
+        <v>-10.33904259615193</v>
       </c>
       <c r="F56">
-        <v>-2.064756429136846</v>
+        <v>-1.679088447211064</v>
       </c>
       <c r="G56">
-        <v>-4.774115699032538</v>
+        <v>-2.361290793645519</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.28966843728549</v>
       </c>
       <c r="E57">
-        <v>-11.77639383160853</v>
+        <v>-9.130501566880898</v>
       </c>
       <c r="F57">
-        <v>-2.338346301463856</v>
+        <v>-1.676196616607891</v>
       </c>
       <c r="G57">
-        <v>-4.964352887901217</v>
+        <v>-3.001374842026985</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.198604500548256</v>
       </c>
       <c r="E58">
-        <v>-9.787718999614098</v>
+        <v>-10.47260088006015</v>
       </c>
       <c r="F58">
-        <v>-2.43843793474412</v>
+        <v>-1.86279548612991</v>
       </c>
       <c r="G58">
-        <v>-4.250857492186412</v>
+        <v>-2.241051779659189</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.082966204631075</v>
       </c>
       <c r="E59">
-        <v>-10.66544141720279</v>
+        <v>-9.237921498816847</v>
       </c>
       <c r="F59">
-        <v>-2.584021849051327</v>
+        <v>-1.746562285638695</v>
       </c>
       <c r="G59">
-        <v>-3.878987222305619</v>
+        <v>-2.482966584395892</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.9422104006613297</v>
       </c>
       <c r="E60">
-        <v>-8.933426906541092</v>
+        <v>-9.241014446564087</v>
       </c>
       <c r="F60">
-        <v>-2.212032698047973</v>
+        <v>-1.502457322646931</v>
       </c>
       <c r="G60">
-        <v>-4.34135125450239</v>
+        <v>-3.082863920476145</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.776854584765704</v>
       </c>
       <c r="E61">
-        <v>-10.6672799776499</v>
+        <v>-9.062488415759697</v>
       </c>
       <c r="F61">
-        <v>-2.491731779970629</v>
+        <v>-1.353202912377919</v>
       </c>
       <c r="G61">
-        <v>-3.530664862845662</v>
+        <v>-3.349942181856848</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.5901281257312651</v>
       </c>
       <c r="E62">
-        <v>-10.84428896966172</v>
+        <v>-7.923196811013958</v>
       </c>
       <c r="F62">
-        <v>-1.395684906263088</v>
+        <v>-1.538963474088305</v>
       </c>
       <c r="G62">
-        <v>-4.936762801376931</v>
+        <v>-2.971543516172612</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.3856206129858109</v>
       </c>
       <c r="E63">
-        <v>-11.83384658134384</v>
+        <v>-7.681430640692454</v>
       </c>
       <c r="F63">
-        <v>-1.799252251028563</v>
+        <v>-1.357821060648526</v>
       </c>
       <c r="G63">
-        <v>-4.659074241542864</v>
+        <v>-3.110804924827594</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.1677345187517542</v>
       </c>
       <c r="E64">
-        <v>-10.53661991710659</v>
+        <v>-7.813390373275968</v>
       </c>
       <c r="F64">
-        <v>-1.887600948006741</v>
+        <v>-1.796435801859045</v>
       </c>
       <c r="G64">
-        <v>-3.894225663422885</v>
+        <v>-3.177091978160421</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.05814877416751048</v>
       </c>
       <c r="E65">
-        <v>-9.11821581689809</v>
+        <v>-8.374762653636823</v>
       </c>
       <c r="F65">
-        <v>-2.771280099025975</v>
+        <v>-1.350727750578354</v>
       </c>
       <c r="G65">
-        <v>-4.766766287935356</v>
+        <v>-3.060418421719886</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.2848618921654367</v>
       </c>
       <c r="E66">
-        <v>-11.38161505304185</v>
+        <v>-8.914452600448953</v>
       </c>
       <c r="F66">
-        <v>-2.835118232922719</v>
+        <v>-1.527175805946468</v>
       </c>
       <c r="G66">
-        <v>-5.476520767190785</v>
+        <v>-2.856704001960834</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.5072200466686185</v>
       </c>
       <c r="E67">
-        <v>-10.21881161124828</v>
+        <v>-7.904054951383536</v>
       </c>
       <c r="F67">
-        <v>-2.53439767141922</v>
+        <v>-1.968077669556116</v>
       </c>
       <c r="G67">
-        <v>-4.656015297464577</v>
+        <v>-2.812329449552443</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.7213253850186455</v>
       </c>
       <c r="E68">
-        <v>-10.27453448391267</v>
+        <v>-7.330261066819641</v>
       </c>
       <c r="F68">
-        <v>-2.285104643383723</v>
+        <v>-1.819895995073729</v>
       </c>
       <c r="G68">
-        <v>-4.488051458984114</v>
+        <v>-2.979121354912004</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.9243018853924159</v>
       </c>
       <c r="E69">
-        <v>-10.72567464997881</v>
+        <v>-8.177665350926979</v>
       </c>
       <c r="F69">
-        <v>-2.508930343987553</v>
+        <v>-1.383415956660225</v>
       </c>
       <c r="G69">
-        <v>-3.892500869196924</v>
+        <v>-2.507080598103943</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.112945208921833</v>
       </c>
       <c r="E70">
-        <v>-8.963776739340499</v>
+        <v>-8.812127201771634</v>
       </c>
       <c r="F70">
-        <v>-2.523802852337415</v>
+        <v>-2.026464317575036</v>
       </c>
       <c r="G70">
-        <v>-4.895857700693696</v>
+        <v>-3.304173889776424</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.286766804870913</v>
       </c>
       <c r="E71">
-        <v>-11.06435469253847</v>
+        <v>-8.162816484655828</v>
       </c>
       <c r="F71">
-        <v>-2.816306837572546</v>
+        <v>-2.099160184109915</v>
       </c>
       <c r="G71">
-        <v>-4.971457318628493</v>
+        <v>-3.187016993687156</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.445722415523299</v>
       </c>
       <c r="E72">
-        <v>-12.01105029773799</v>
+        <v>-7.904507798784303</v>
       </c>
       <c r="F72">
-        <v>-2.666859417698681</v>
+        <v>-2.162903055755337</v>
       </c>
       <c r="G72">
-        <v>-3.285002520558504</v>
+        <v>-2.905657038850037</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.589599578433871</v>
       </c>
       <c r="E73">
-        <v>-8.104539552651119</v>
+        <v>-8.392464458532807</v>
       </c>
       <c r="F73">
-        <v>-3.093985531399773</v>
+        <v>-2.391323710342495</v>
       </c>
       <c r="G73">
-        <v>-3.451695109551887</v>
+        <v>-2.678278839576274</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.716729601748197</v>
       </c>
       <c r="E74">
-        <v>-9.888328106642509</v>
+        <v>-9.08884413448434</v>
       </c>
       <c r="F74">
-        <v>-2.777330494536023</v>
+        <v>-2.406966600376961</v>
       </c>
       <c r="G74">
-        <v>-4.510016928637179</v>
+        <v>-2.891411761394553</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.826885933314294</v>
       </c>
       <c r="E75">
-        <v>-10.94681814966939</v>
+        <v>-9.210610272076588</v>
       </c>
       <c r="F75">
-        <v>-3.189898879500317</v>
+        <v>-2.268685573092834</v>
       </c>
       <c r="G75">
-        <v>-4.310877682813399</v>
+        <v>-2.010843063949349</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.91869616394347</v>
       </c>
       <c r="E76">
-        <v>-11.54877008561298</v>
+        <v>-8.91783989900669</v>
       </c>
       <c r="F76">
-        <v>-3.023144379479762</v>
+        <v>-2.759591834972474</v>
       </c>
       <c r="G76">
-        <v>-5.166071048700089</v>
+        <v>-2.857190652155107</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.989897625773857</v>
       </c>
       <c r="E77">
-        <v>-13.07672702901504</v>
+        <v>-10.13535636376093</v>
       </c>
       <c r="F77">
-        <v>-3.078124780738371</v>
+        <v>-2.598467748188748</v>
       </c>
       <c r="G77">
-        <v>-2.919488498113112</v>
+        <v>-2.6177455143907</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.03728077421746</v>
       </c>
       <c r="E78">
-        <v>-11.56743645547259</v>
+        <v>-11.34725299227165</v>
       </c>
       <c r="F78">
-        <v>-2.537948882475022</v>
+        <v>-2.922466262078316</v>
       </c>
       <c r="G78">
-        <v>-3.201513872603624</v>
+        <v>-2.578058694465917</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.059591084799828</v>
       </c>
       <c r="E79">
-        <v>-12.6062231080921</v>
+        <v>-11.61287063519155</v>
       </c>
       <c r="F79">
-        <v>-3.398060152517207</v>
+        <v>-2.855697364310467</v>
       </c>
       <c r="G79">
-        <v>-3.095655868439889</v>
+        <v>-2.165882532644498</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.055250456400808</v>
       </c>
       <c r="E80">
-        <v>-14.07479364335757</v>
+        <v>-11.27400492519758</v>
       </c>
       <c r="F80">
-        <v>-3.268166345186425</v>
+        <v>-2.901964997226431</v>
       </c>
       <c r="G80">
-        <v>-3.241015301978208</v>
+        <v>-2.816964213307422</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.023142820706259</v>
       </c>
       <c r="E81">
-        <v>-14.00114707057083</v>
+        <v>-11.7419004450921</v>
       </c>
       <c r="F81">
-        <v>-3.135253138672439</v>
+        <v>-2.722405593893402</v>
       </c>
       <c r="G81">
-        <v>-2.961049086813123</v>
+        <v>-1.93216463866303</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.963161037071259</v>
       </c>
       <c r="E82">
-        <v>-14.46096379283567</v>
+        <v>-12.42880655341959</v>
       </c>
       <c r="F82">
-        <v>-3.363003644030732</v>
+        <v>-2.524212894201801</v>
       </c>
       <c r="G82">
-        <v>-3.786285326114948</v>
+        <v>-1.462987503746439</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.877895683920102</v>
       </c>
       <c r="E83">
-        <v>-15.34990324054136</v>
+        <v>-15.08272780256282</v>
       </c>
       <c r="F83">
-        <v>-3.902916949827394</v>
+        <v>-3.040067097151554</v>
       </c>
       <c r="G83">
-        <v>-3.698979619153288</v>
+        <v>-1.853813957385099</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.769792960801946</v>
       </c>
       <c r="E84">
-        <v>-16.86325585526869</v>
+        <v>-14.70043855530929</v>
       </c>
       <c r="F84">
-        <v>-3.733292985123542</v>
+        <v>-3.363929758787062</v>
       </c>
       <c r="G84">
-        <v>-3.358460215529393</v>
+        <v>-1.851950120246489</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.641432911083304</v>
       </c>
       <c r="E85">
-        <v>-16.48510110478416</v>
+        <v>-15.86337785132309</v>
       </c>
       <c r="F85">
-        <v>-3.534127782101054</v>
+        <v>-3.209230489579449</v>
       </c>
       <c r="G85">
-        <v>-2.883271129913485</v>
+        <v>-0.7133839878348035</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.495939544795839</v>
       </c>
       <c r="E86">
-        <v>-18.49212078498367</v>
+        <v>-17.74178434123074</v>
       </c>
       <c r="F86">
-        <v>-3.970495990915181</v>
+        <v>-3.487926418577314</v>
       </c>
       <c r="G86">
-        <v>-3.753510925276163</v>
+        <v>-1.107511055376117</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.33849988542531</v>
       </c>
       <c r="E87">
-        <v>-20.80203197766021</v>
+        <v>-18.51385293174648</v>
       </c>
       <c r="F87">
-        <v>-4.497417182366335</v>
+        <v>-3.59040043650803</v>
       </c>
       <c r="G87">
-        <v>-2.21506399717591</v>
+        <v>-1.332886374598621</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.173755996530531</v>
       </c>
       <c r="E88">
-        <v>-21.39925165826578</v>
+        <v>-20.41469801036214</v>
       </c>
       <c r="F88">
-        <v>-4.038070061798551</v>
+        <v>-3.031254924720572</v>
       </c>
       <c r="G88">
-        <v>-3.305574250539536</v>
+        <v>-0.6690326092451874</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.00680594193248</v>
       </c>
       <c r="E89">
-        <v>-21.08649712940004</v>
+        <v>-21.61564478872231</v>
       </c>
       <c r="F89">
-        <v>-4.134579006061706</v>
+        <v>-3.614004765650802</v>
       </c>
       <c r="G89">
-        <v>-2.15787763353054</v>
+        <v>-1.899535901827973</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.843174606319215</v>
       </c>
       <c r="E90">
-        <v>-22.69588056393402</v>
+        <v>-23.24533390070669</v>
       </c>
       <c r="F90">
-        <v>-3.957165902669331</v>
+        <v>-3.995249265645635</v>
       </c>
       <c r="G90">
-        <v>-3.215729355149255</v>
+        <v>-1.59343955072142</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.6908790811337111</v>
       </c>
       <c r="E91">
-        <v>-23.56528870324463</v>
+        <v>-23.77171919088428</v>
       </c>
       <c r="F91">
-        <v>-3.711238531391408</v>
+        <v>-4.003397915786974</v>
       </c>
       <c r="G91">
-        <v>-2.313082629502651</v>
+        <v>-1.720971696530764</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.5567982306502864</v>
       </c>
       <c r="E92">
-        <v>-25.58171402395806</v>
+        <v>-25.70422283128757</v>
       </c>
       <c r="F92">
-        <v>-4.592049046094748</v>
+        <v>-4.240947179152982</v>
       </c>
       <c r="G92">
-        <v>-3.465817896822418</v>
+        <v>-1.927930450918302</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.4473790250094296</v>
       </c>
       <c r="E93">
-        <v>-27.69872580932987</v>
+        <v>-27.7025206705483</v>
       </c>
       <c r="F93">
-        <v>-4.842395757466606</v>
+        <v>-4.622531309782964</v>
       </c>
       <c r="G93">
-        <v>-2.855157977193994</v>
+        <v>-2.676908273723016</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.3675241239536227</v>
       </c>
       <c r="E94">
-        <v>-30.0233862418494</v>
+        <v>-29.08463358005933</v>
       </c>
       <c r="F94">
-        <v>-4.952291947326405</v>
+        <v>-4.356937667995178</v>
       </c>
       <c r="G94">
-        <v>-3.367653600491949</v>
+        <v>-1.713185293422398</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.3228732458870553</v>
       </c>
       <c r="E95">
-        <v>-31.49713055866863</v>
+        <v>-31.49312965188286</v>
       </c>
       <c r="F95">
-        <v>-5.087246251120889</v>
+        <v>-4.461721174244898</v>
       </c>
       <c r="G95">
-        <v>-3.746595195644626</v>
+        <v>-2.330317329580097</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.3163434380029127</v>
       </c>
       <c r="E96">
-        <v>-33.52287774312686</v>
+        <v>-33.256109867809</v>
       </c>
       <c r="F96">
-        <v>-5.093053106614514</v>
+        <v>-4.845271020721722</v>
       </c>
       <c r="G96">
-        <v>-4.357407400367856</v>
+        <v>-3.116485820972983</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.3466980237962289</v>
       </c>
       <c r="E97">
-        <v>-36.01050436976041</v>
+        <v>-35.45883660919799</v>
       </c>
       <c r="F97">
-        <v>-5.305410060526584</v>
+        <v>-4.993547957455432</v>
       </c>
       <c r="G97">
-        <v>-4.69461625845248</v>
+        <v>-2.308212817014384</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.4128854231272218</v>
       </c>
       <c r="E98">
-        <v>-38.50785363008844</v>
+        <v>-37.0900133248939</v>
       </c>
       <c r="F98">
-        <v>-5.459221319878396</v>
+        <v>-5.16650278748594</v>
       </c>
       <c r="G98">
-        <v>-5.44242545868183</v>
+        <v>-3.418784976345993</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.5097727160426674</v>
       </c>
       <c r="E99">
-        <v>-40.32077838584518</v>
+        <v>-39.52009889654899</v>
       </c>
       <c r="F99">
-        <v>-5.780284099692443</v>
+        <v>-5.237903915770244</v>
       </c>
       <c r="G99">
-        <v>-5.218096271849736</v>
+        <v>-3.548376281480763</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.6381567453582165</v>
       </c>
       <c r="E100">
-        <v>-42.35398849546804</v>
+        <v>-42.20122268905629</v>
       </c>
       <c r="F100">
-        <v>-5.654511420190588</v>
+        <v>-5.879467013931835</v>
       </c>
       <c r="G100">
-        <v>-5.814269244198309</v>
+        <v>-4.419298049224531</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.7853383758528403</v>
       </c>
       <c r="E101">
-        <v>-43.55517528295063</v>
+        <v>-43.9412118424455</v>
       </c>
       <c r="F101">
-        <v>-5.839818864931643</v>
+        <v>-5.629700159741937</v>
       </c>
       <c r="G101">
-        <v>-6.020724795663878</v>
+        <v>-4.14366864871589</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.9591699099776175</v>
       </c>
       <c r="E102">
-        <v>-45.49131075950806</v>
+        <v>-45.41057033218831</v>
       </c>
       <c r="F102">
-        <v>-6.378317733388024</v>
+        <v>-5.685040900820764</v>
       </c>
       <c r="G102">
-        <v>-6.087902385746769</v>
+        <v>-4.034523272831659</v>
       </c>
     </row>
   </sheetData>
